--- a/docs/DecisionOS_Epic3_Dex_AI_Persona.xlsx
+++ b/docs/DecisionOS_Epic3_Dex_AI_Persona.xlsx
@@ -543,7 +543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -572,7 +572,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Epic 3 progress: 0 of 8 items Done  (0%)</t>
+          <t>Epic 3 progress: 0 of 13 items Done  (0%)</t>
         </is>
       </c>
     </row>
@@ -709,6 +709,39 @@
       <c r="G8" s="7" t="inlineStr">
         <is>
           <t>Decide the role/persona nav question. What is the DEFAULT landing tab for Sales vs Production vs Finance vs Owner? Should nav reorder-per-role or hide-per-role? Ships as either tenant-level config (owner picks) or system defaults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="40" customHeight="1">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Dex knowledge + retrieval</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>Ingest-time embeddings, RAG, agent loop, agent memory, auto-assign</t>
         </is>
       </c>
     </row>
@@ -800,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1019,6 +1052,49 @@
       <c r="B28" s="14" t="inlineStr">
         <is>
           <t>Decide the role/persona nav question. What is the DEFAULT landing tab for Sales vs Production vs Finance vs Owner? Should nav reorder-per-role or hide-per-role? Ships as either tenant-level config (owner picks) or system defaults.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 4 -- Dex knowledge + retrieval</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Backlog (imported from Stability tracker 2026-08-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>E3-09, E3-10, E3-11, E3-12, E3-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="100" customHeight="1">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Sprint 4 -- Dex knowledge + retrieval (5 items imported from Epic 1 Stability tracker on 2026-08-15). Ingest-time document extraction + chunk + embed, vector search + hybrid retrieval, bounded planner-executor loop with native function-calling, per-conversation agent memory, auto-assign AI-generated tasks. Sits alongside the persona work in Sprint 1-3 -- this sprint is the 'how does Dex actually know things' layer.</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1558,6 +1634,276 @@
       <c r="L9" s="18" t="inlineStr">
         <is>
           <t>Epic 2 close-out 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="180" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>E3-09</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr"/>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
+        <is>
+          <t>AI/Brain</t>
+        </is>
+      </c>
+      <c r="E10" s="16" t="inlineStr">
+        <is>
+          <t>Extract + chunk + embed documents at ingest</t>
+        </is>
+      </c>
+      <c r="F10" s="16" t="inlineStr">
+        <is>
+          <t>Uploaded documents are stored as metadata only; body text is never read at ingest. Add server-side extraction + chunking + embeddings into a new brain_chunks collection.</t>
+        </is>
+      </c>
+      <c r="G10" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J10" s="16" t="inlineStr"/>
+      <c r="K10" s="16" t="inlineStr">
+        <is>
+          <t>Imported from Stability tracker S4-05. Origin sprint: Sprint 4. File ref: routers/brain_docs.py:147-213</t>
+        </is>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>Stability tracker split 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="180" customHeight="1">
+      <c r="A11" s="18" t="inlineStr">
+        <is>
+          <t>E3-10</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>AI/Brain</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="inlineStr">
+        <is>
+          <t>Adopt vector search + hybrid retrieval</t>
+        </is>
+      </c>
+      <c r="F11" s="18" t="inlineStr">
+        <is>
+          <t>Move from keyword-only BM25/regex to embeddings (Atlas Vector Search if on Atlas, else Qdrant/pgvector) fused with existing text search.</t>
+        </is>
+      </c>
+      <c r="G11" s="18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H11" s="18" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J11" s="18" t="inlineStr"/>
+      <c r="K11" s="18" t="inlineStr">
+        <is>
+          <t>Imported from Stability tracker S4-06. Origin sprint: Sprint 4. File ref: (new infra)</t>
+        </is>
+      </c>
+      <c r="L11" s="18" t="inlineStr">
+        <is>
+          <t>Stability tracker split 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="180" customHeight="1">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>E3-11</t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr"/>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>AI/Brain</t>
+        </is>
+      </c>
+      <c r="E12" s="16" t="inlineStr">
+        <is>
+          <t>Add bounded planner-executor loop + native function-calling</t>
+        </is>
+      </c>
+      <c r="F12" s="16" t="inlineStr">
+        <is>
+          <t>/brain/agent is single-turn (plan -&gt; fan-out -&gt; synthesize, no re-plan). Add an observe-then-replan loop and migrate to Anthropic tools=[...].</t>
+        </is>
+      </c>
+      <c r="G12" s="16" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J12" s="16" t="inlineStr"/>
+      <c r="K12" s="16" t="inlineStr">
+        <is>
+          <t>Imported from Stability tracker S4-08. Origin sprint: Sprint 4. File ref: routers/brain_router.py:266-277,481-482</t>
+        </is>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>Stability tracker split 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="180" customHeight="1">
+      <c r="A13" s="18" t="inlineStr">
+        <is>
+          <t>E3-12</t>
+        </is>
+      </c>
+      <c r="B13" s="18" t="inlineStr"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>AI/Brain</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="inlineStr">
+        <is>
+          <t>Add per-conversation agent memory</t>
+        </is>
+      </c>
+      <c r="F13" s="18" t="inlineStr">
+        <is>
+          <t>Every LLM call gets a fresh random session_id; planner and synthesizer don't even share context.</t>
+        </is>
+      </c>
+      <c r="G13" s="18" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H13" s="18" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="inlineStr"/>
+      <c r="K13" s="18" t="inlineStr">
+        <is>
+          <t>Imported from Stability tracker S4-09. Origin sprint: Sprint 4. File ref: routers/brain_router.py:95,353</t>
+        </is>
+      </c>
+      <c r="L13" s="18" t="inlineStr">
+        <is>
+          <t>Stability tracker split 2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="180" customHeight="1">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>E3-13</t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr"/>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t>AI / Task routing</t>
+        </is>
+      </c>
+      <c r="E14" s="16" t="inlineStr">
+        <is>
+          <t>Auto-assign AI-generated tasks when one user matches the role</t>
+        </is>
+      </c>
+      <c r="F14" s="16" t="inlineStr">
+        <is>
+          <t>AI sets assignee_role but leaves assignee_id null. For tenants with 1 person per role, auto-assign deterministically. For 2+ show a 'pick a person' chip. For 0 fall back to owner + notify.</t>
+        </is>
+      </c>
+      <c r="G14" s="16" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="H14" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I14" s="17" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="J14" s="16" t="inlineStr"/>
+      <c r="K14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Imported from Stability tracker FUP-47. Origin sprint: Follow-up. File ref: </t>
+        </is>
+      </c>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>Stability tracker split 2026-08-15</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic3_Dex_AI_Persona.xlsx
+++ b/docs/DecisionOS_Epic3_Dex_AI_Persona.xlsx
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B33"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1093,6 +1093,49 @@
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Sprint 4 -- Dex knowledge + retrieval (5 items imported from Epic 1 Stability tracker on 2026-08-15). Ingest-time document extraction + chunk + embed, vector search + hybrid retrieval, bounded planner-executor loop with native function-calling, per-conversation agent memory, auto-assign AI-generated tasks. Sits alongside the persona work in Sprint 1-3 -- this sprint is the 'how does Dex actually know things' layer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 4 -- Dex knowledge + retrieval</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Backlog (imported from Stability tracker 2026-08-15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Items</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>E3-09, E3-10, E3-11, E3-12, E3-13</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="100" customHeight="1">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
         <is>
           <t>Sprint 4 -- Dex knowledge + retrieval (5 items imported from Epic 1 Stability tracker on 2026-08-15). Ingest-time document extraction + chunk + embed, vector search + hybrid retrieval, bounded planner-executor loop with native function-calling, per-conversation agent memory, auto-assign AI-generated tasks. Sits alongside the persona work in Sprint 1-3 -- this sprint is the 'how does Dex actually know things' layer.</t>
         </is>
@@ -1907,6 +1950,11 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="180" customHeight="1"/>
+    <row r="16" ht="180" customHeight="1"/>
+    <row r="17" ht="180" customHeight="1"/>
+    <row r="18" ht="180" customHeight="1"/>
+    <row r="19" ht="180" customHeight="1"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
